--- a/tools/importer/reports/import-department-landing.report.xlsx
+++ b/tools/importer/reports/import-department-landing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="82">
   <si>
     <t>_reportFile</t>
   </si>
@@ -199,6 +199,24 @@
     <t>http://localhost:8082/lsa/prospective-students.html</t>
   </si>
   <si>
+    <t>urop/prospective-students.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>urop/prospective-students</t>
+  </si>
+  <si>
+    <t>2026-08-14T15:54:22.361Z</t>
+  </si>
+  <si>
+    <t>Prospective UROP Students | U-M LSA UROP: A Center for Research, Scholarship, and Creative Inquiry</t>
+  </si>
+  <si>
+    <t>http://localhost:8082/urop/prospective-students.html</t>
+  </si>
+  <si>
     <t>lsa/academics/departments-and-units.html.report.json</t>
   </si>
   <si>
@@ -225,9 +243,6 @@
   </si>
   <si>
     <t>lsa/academics/departments-and-units.report.json</t>
-  </si>
-  <si>
-    <t>[]</t>
   </si>
   <si>
     <t>lsa/academics/departments-and-units</t>
@@ -643,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="50" customWidth="1"/>
@@ -974,31 +989,31 @@
         <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
         <v>62</v>
       </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" t="s">
         <v>63</v>
       </c>
-      <c r="G10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>64</v>
-      </c>
-      <c r="J10" t="s">
-        <v>12</v>
       </c>
       <c r="K10" t="s">
         <v>65</v>
@@ -1009,34 +1024,34 @@
         <v>66</v>
       </c>
       <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
         <v>67</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="I11" t="s">
         <v>70</v>
       </c>
       <c r="J11" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" t="s">
         <v>71</v>
-      </c>
-      <c r="K11" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1044,7 +1059,7 @@
         <v>72</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -1062,16 +1077,51 @@
         <v>22</v>
       </c>
       <c r="H12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" t="s">
         <v>74</v>
       </c>
-      <c r="J12" t="s">
-        <v>75</v>
-      </c>
-      <c r="K12" t="s">
-        <v>76</v>
+      <c r="I13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-department-landing.report.xlsx
+++ b/tools/importer/reports/import-department-landing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="87">
   <si>
     <t>_reportFile</t>
   </si>
@@ -270,6 +270,21 @@
   </si>
   <si>
     <t>http://localhost:8082/lsa/academics/majors-minors.html</t>
+  </si>
+  <si>
+    <t>psych/prospective-students/undergraduate.report.json</t>
+  </si>
+  <si>
+    <t>psych/prospective-students/undergraduate</t>
+  </si>
+  <si>
+    <t>2026-08-14T15:57:49.068Z</t>
+  </si>
+  <si>
+    <t>Undergraduate | U-M LSA Department of Psychology</t>
+  </si>
+  <si>
+    <t>http://localhost:8082/psych/prospective-students/undergraduate.html</t>
   </si>
 </sst>
 </file>
@@ -658,7 +673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="50" customWidth="1"/>
@@ -1124,6 +1139,41 @@
         <v>81</v>
       </c>
     </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J14" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/importer/reports/import-department-landing.report.xlsx
+++ b/tools/importer/reports/import-department-landing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>_reportFile</t>
   </si>
@@ -46,10 +46,34 @@
     <t>url</t>
   </si>
   <si>
+    <t>cgis.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>cgis</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>department-landing</t>
+  </si>
+  <si>
+    <t>2026-08-14T16:02:54.342Z</t>
+  </si>
+  <si>
+    <t>Center for Global and Intercultural Study | U-M LSA</t>
+  </si>
+  <si>
+    <t>http://localhost:8082/cgis.html</t>
+  </si>
+  <si>
     <t>header-footer-source.html.report.json</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t xml:space="preserve">page.evaluate: Error: Failed to import page: Cannot read properties of undefined (reading 'replace')
@@ -85,9 +109,6 @@
     <t>home</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>homepage</t>
   </si>
   <si>
@@ -166,9 +187,6 @@
     <t>english/undergraduate</t>
   </si>
   <si>
-    <t>department-landing</t>
-  </si>
-  <si>
     <t>2026-08-14T15:35:10.407Z</t>
   </si>
   <si>
@@ -200,9 +218,6 @@
   </si>
   <si>
     <t>urop/prospective-students.report.json</t>
-  </si>
-  <si>
-    <t>[]</t>
   </si>
   <si>
     <t>urop/prospective-students</t>
@@ -673,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="50" customWidth="1"/>
@@ -730,60 +745,60 @@
         <v>13</v>
       </c>
       <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K3" t="s">
         <v>26</v>
@@ -794,66 +809,66 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
         <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" t="s">
-        <v>36</v>
       </c>
       <c r="K5" t="s">
         <v>37</v>
@@ -864,104 +879,104 @@
         <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
         <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J6" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="K6" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J8" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -972,57 +987,57 @@
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
         <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" t="s">
         <v>56</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>57</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>58</v>
-      </c>
-      <c r="K9" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
         <v>60</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
         <v>61</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
         <v>62</v>
-      </c>
-      <c r="G10" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" t="s">
-        <v>49</v>
       </c>
       <c r="I10" t="s">
         <v>63</v>
@@ -1042,66 +1057,66 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
         <v>67</v>
       </c>
-      <c r="D11" t="s">
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
         <v>68</v>
       </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="J11" t="s">
         <v>69</v>
       </c>
-      <c r="G11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>70</v>
-      </c>
-      <c r="J11" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
         <v>72</v>
       </c>
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="I12" t="s">
         <v>75</v>
       </c>
       <c r="J12" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" t="s">
         <v>76</v>
-      </c>
-      <c r="K12" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1109,34 +1124,34 @@
         <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
         <v>78</v>
       </c>
       <c r="G13" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1144,25 +1159,25 @@
         <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
         <v>83</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s">
         <v>84</v>
@@ -1172,6 +1187,41 @@
       </c>
       <c r="K14" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s">
+        <v>89</v>
+      </c>
+      <c r="J15" t="s">
+        <v>90</v>
+      </c>
+      <c r="K15" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
